--- a/content/tz-vk/tz-kitajskij-chaj.xlsx
+++ b/content/tz-vk/tz-kitajskij-chaj.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -867,6 +867,91 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ВАЖНО: 黑茶 (hēichá) = «чёрный чай» (постферментированный, к нему относится пуэр); 红茶 (hóngchá) = «красный», на Западе его зовут «чёрным»</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>6 видов / уточнение</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Чай — основа неформальной беседы и часто фон деловых переговоров; помогает влиться в общество и даёт тему для языковой практики</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Зачем это</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Китайцы ценят иностранцев, понимающих их культуру, — это повышает доверие и лояльность (в т.ч. в бизнесе)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Зачем это</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Церемония гунфу-ча тренирует внимание и присутствие «здесь и сейчас» — дисциплина и концентрация</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Зачем это</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Через чай удобно изучать историю Китая и мира — он не раз влиял на крупные события (шёлковый путь, торговля)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Зачем это</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
